--- a/data/projects/drum-poc/raw/드럼POC_샘플.xlsx
+++ b/data/projects/drum-poc/raw/드럼POC_샘플.xlsx
@@ -1305,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1425,7 +1425,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1453,12 +1453,90 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>토크 암 보강 반영 후 런 재개</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-11</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>무발생 검증 병행</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/projects/drum-poc/raw/드럼POC_샘플.xlsx
+++ b/data/projects/drum-poc/raw/드럼POC_샘플.xlsx
@@ -546,12 +546,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -590,12 +590,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -634,12 +634,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -678,12 +678,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -722,12 +722,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
@@ -766,12 +766,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -810,12 +810,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -854,12 +854,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
@@ -898,12 +898,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -942,12 +942,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -986,12 +986,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1030,7 +1030,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -1339,7 +1339,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -1357,7 +1357,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -1371,7 +1371,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -1389,7 +1389,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -1407,7 +1407,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -1421,7 +1421,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -1435,7 +1435,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -1449,7 +1449,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -1463,7 +1463,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -1477,7 +1477,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -1495,7 +1495,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -1509,7 +1509,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -1523,7 +1523,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7/10 예정</t>
+          <t>07-17 예정</t>
         </is>
       </c>
     </row>
